--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2019_los_lagos_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2019_los_lagos_provincial.xlsx
@@ -52,7 +52,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 23:09</t>
+    <t xml:space="preserve">2026-09-29 14:03</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2019_los_lagos_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2019_los_lagos_provincial.xlsx
@@ -52,7 +52,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 14:03</t>
+    <t xml:space="preserve">2026-09-29 18:36</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -521,10 +521,10 @@
         <v>-1.64</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>27.87</v>
+        <v>27.88</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>29.51</v>
+        <v>29.52</v>
       </c>
     </row>
     <row r="5">
@@ -538,7 +538,7 @@
         <v>56.87</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>58.59</v>
+        <v>58.58</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2019_los_lagos_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2019_los_lagos_provincial.xlsx
@@ -52,7 +52,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 18:36</t>
+    <t xml:space="preserve">2026-10-05 04:02</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -538,7 +538,7 @@
         <v>56.87</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>58.58</v>
+        <v>58.59</v>
       </c>
     </row>
   </sheetData>
